--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/MergeMoves.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/MergeMoves.xlsx
@@ -35,7 +35,21 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="1">
+  <x:fonts count="3">
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -406,6 +420,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
+      <x:c r="B1" s="0" t="s"/>
       <x:c r="F1" s="0" t="s"/>
       <x:c r="G1" s="0" t="s"/>
       <x:c r="H1" s="0" t="s"/>
@@ -483,6 +498,7 @@
       <x:c r="A9" s="0" t="s"/>
       <x:c r="B9" s="0" t="s"/>
       <x:c r="E9" s="0" t="s"/>
+      <x:c r="F9" s="0" t="s"/>
       <x:c r="G9" s="0" t="s"/>
       <x:c r="H9" s="0" t="s"/>
     </x:row>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/MergeMoves.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/MergeMoves.xlsx
@@ -420,7 +420,6 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
-      <x:c r="B1" s="0" t="s"/>
       <x:c r="F1" s="0" t="s"/>
       <x:c r="G1" s="0" t="s"/>
       <x:c r="H1" s="0" t="s"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/MergeMoves.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/MergeMoves.xlsx
@@ -86,38 +86,38 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="7">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="3">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/MergeMoves.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/MergeMoves.xlsx
@@ -419,94 +419,31 @@
   <x:dimension ref="A1:F8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:9">
-      <x:c r="F1" s="0" t="s"/>
-      <x:c r="G1" s="0" t="s"/>
-      <x:c r="H1" s="0" t="s"/>
-      <x:c r="I1" s="0" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:9">
-      <x:c r="A2" s="0" t="s"/>
+    <x:row r="1" spans="1:6"/>
+    <x:row r="2" spans="1:6">
       <x:c r="B2" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s"/>
-      <x:c r="D2" s="0" t="s"/>
       <x:c r="F2" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s"/>
-      <x:c r="H2" s="0" t="s"/>
-      <x:c r="I2" s="0" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:9">
-      <x:c r="A3" s="0" t="s"/>
-      <x:c r="B3" s="0" t="s"/>
-      <x:c r="C3" s="0" t="s"/>
-      <x:c r="D3" s="0" t="s"/>
-      <x:c r="E3" s="0" t="s"/>
-      <x:c r="G3" s="0" t="s"/>
-      <x:c r="H3" s="0" t="s"/>
-      <x:c r="I3" s="0" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:9">
-      <x:c r="A4" s="0" t="s"/>
+    <x:row r="3" spans="1:6"/>
+    <x:row r="4" spans="1:6">
       <x:c r="B4" s="2" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s"/>
-      <x:c r="G4" s="0" t="s"/>
-      <x:c r="H4" s="0" t="s"/>
-      <x:c r="I4" s="0" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:9">
-      <x:c r="A5" s="0" t="s"/>
-      <x:c r="B5" s="0" t="s"/>
-      <x:c r="C5" s="0" t="s"/>
-      <x:c r="D5" s="0" t="s"/>
-      <x:c r="E5" s="0" t="s"/>
-      <x:c r="F5" s="0" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:9">
-      <x:c r="A6" s="0" t="s"/>
-      <x:c r="B6" s="0" t="s"/>
-      <x:c r="C6" s="0" t="s"/>
-      <x:c r="D6" s="0" t="s"/>
-      <x:c r="E6" s="0" t="s"/>
-      <x:c r="F6" s="0" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:9">
-      <x:c r="A7" s="0" t="s"/>
-      <x:c r="B7" s="0" t="s"/>
-      <x:c r="C7" s="0" t="s"/>
-      <x:c r="D7" s="0" t="s"/>
-      <x:c r="E7" s="0" t="s"/>
-      <x:c r="F7" s="0" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:9">
-      <x:c r="A8" s="0" t="s"/>
+    <x:row r="5" spans="1:6"/>
+    <x:row r="6" spans="1:6"/>
+    <x:row r="7" spans="1:6"/>
+    <x:row r="8" spans="1:6">
       <x:c r="B8" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s"/>
-      <x:c r="E8" s="0" t="s"/>
-      <x:c r="G8" s="0" t="s"/>
-      <x:c r="H8" s="0" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:9">
-      <x:c r="A9" s="0" t="s"/>
-      <x:c r="B9" s="0" t="s"/>
-      <x:c r="E9" s="0" t="s"/>
-      <x:c r="F9" s="0" t="s"/>
-      <x:c r="G9" s="0" t="s"/>
-      <x:c r="H9" s="0" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:9">
-      <x:c r="A10" s="0" t="s"/>
-      <x:c r="B10" s="0" t="s"/>
-      <x:c r="D10" s="0" t="s"/>
-      <x:c r="E10" s="0" t="s"/>
-    </x:row>
+    <x:row r="9" spans="1:6"/>
+    <x:row r="10" spans="1:6"/>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
